--- a/artfynd/A 57427-2024 artfynd.xlsx
+++ b/artfynd/A 57427-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>58219880</v>
+        <v>58219876</v>
       </c>
       <c r="B2" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,19 +705,19 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Klovstenalund 5250/5450, Nrk</t>
+          <t>Klovstenalund 5050/5450, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511926.6210430731</v>
+        <v>511929</v>
       </c>
       <c r="R2" t="n">
-        <v>6523134.41121034</v>
+        <v>6522934</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -752,24 +747,9 @@
           <t>1982-07-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1982-07-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>5+1 ex</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>58219876</v>
+        <v>58219880</v>
       </c>
       <c r="B3" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,19 +806,19 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Klovstenalund 5050/5450, Nrk</t>
+          <t>Klovstenalund 5250/5450, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511928.7944529766</v>
+        <v>511927</v>
       </c>
       <c r="R3" t="n">
-        <v>6522934.160667752</v>
+        <v>6523134</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -873,19 +848,14 @@
           <t>1982-07-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1982-07-08</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>5+1 ex</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 57427-2024 artfynd.xlsx
+++ b/artfynd/A 57427-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58219876</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,8 +889,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58219880</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>